--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\Fase 2\Sprint Backlogs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\SIGMA\Fase 2\Sprint Backlogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07587FE5-0E98-4BDC-8574-38214248313C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3891E5DC-974A-4814-93A4-0E1DF3D73FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2305" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="644">
   <si>
     <t>Sprint Backlog · Sprint 6</t>
   </si>
@@ -692,162 +692,144 @@
     <t>Datos de prueba en Orden_Trabajo para poder ejercitar los criterios de aceptación.</t>
   </si>
   <si>
-    <t>T-6018</t>
-  </si>
-  <si>
-    <t>POST /api/orden-trabajo-predicciones — dispara el proceso y devuelve su resultado.</t>
-  </si>
-  <si>
-    <t>T-6019</t>
+    <t>T-6020</t>
+  </si>
+  <si>
+    <t>Pantalla OrdenTrabajoPrediccion.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
+  </si>
+  <si>
+    <t>T-6021</t>
+  </si>
+  <si>
+    <t>T-6022</t>
+  </si>
+  <si>
+    <t>T-6023</t>
+  </si>
+  <si>
+    <t>T-6024</t>
+  </si>
+  <si>
+    <t>T-6025</t>
+  </si>
+  <si>
+    <t>SP SEL_PREDICCION_EXPLICACION: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
+  </si>
+  <si>
+    <t>T-6026</t>
+  </si>
+  <si>
+    <t>T-6027</t>
+  </si>
+  <si>
+    <t>T-6028</t>
+  </si>
+  <si>
+    <t>GET /api/predicciones/{id}/explicacion — consulta con filtros y paginación.</t>
+  </si>
+  <si>
+    <t>T-6029</t>
+  </si>
+  <si>
+    <t>T-6030</t>
+  </si>
+  <si>
+    <t>Pantalla PrediccionExplicacion.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
+  </si>
+  <si>
+    <t>T-6031</t>
+  </si>
+  <si>
+    <t>T-6032</t>
+  </si>
+  <si>
+    <t>T-6033</t>
+  </si>
+  <si>
+    <t>T-6034</t>
+  </si>
+  <si>
+    <t>T-6035</t>
+  </si>
+  <si>
+    <t>Modelo: CREAR la tabla Indicador_Valor — todavía no existe. Columnas, PK, FK a sus padres y columna ind_uuid con índice UNIQUE para que la sincronización no duplique.</t>
+  </si>
+  <si>
+    <t>T-6036</t>
+  </si>
+  <si>
+    <t>SP SEL_INDICADOR_TABLERO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
+  </si>
+  <si>
+    <t>T-6037</t>
+  </si>
+  <si>
+    <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Indicador_Valor crezca.</t>
+  </si>
+  <si>
+    <t>T-6038</t>
+  </si>
+  <si>
+    <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
+  </si>
+  <si>
+    <t>T-6041</t>
+  </si>
+  <si>
+    <t>Pantalla IndicadorTablero.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
+  </si>
+  <si>
+    <t>T-6042</t>
+  </si>
+  <si>
+    <t>T-6043</t>
+  </si>
+  <si>
+    <t>T-6044</t>
+  </si>
+  <si>
+    <t>T-6045</t>
+  </si>
+  <si>
+    <t>T-6046</t>
+  </si>
+  <si>
+    <t>Modelo: revisar Alerta — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
+  </si>
+  <si>
+    <t>T-6047</t>
+  </si>
+  <si>
+    <t>SP ALERTA_PREDICCION: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
+  </si>
+  <si>
+    <t>T-6048</t>
+  </si>
+  <si>
+    <t>T-6049</t>
+  </si>
+  <si>
+    <t>SP SEL_ALERTA_PREDICCION: consultar el resultado del proceso.</t>
+  </si>
+  <si>
+    <t>T-6050</t>
+  </si>
+  <si>
+    <t>Datos de prueba en Alerta para poder ejercitar los criterios de aceptación.</t>
+  </si>
+  <si>
+    <t>T-6051</t>
+  </si>
+  <si>
+    <t>POST /api/alerta-predicciones — dispara el proceso y devuelve su resultado.</t>
+  </si>
+  <si>
+    <t>T-6052</t>
   </si>
   <si>
     <t>Manejo de errores del SP: cada RAISERROR se traduce a un código HTTP con mensaje, no a un 500 genérico.</t>
   </si>
   <si>
-    <t>T-6020</t>
-  </si>
-  <si>
-    <t>Pantalla OrdenTrabajoPrediccion.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
-  </si>
-  <si>
-    <t>T-6021</t>
-  </si>
-  <si>
-    <t>T-6022</t>
-  </si>
-  <si>
-    <t>T-6023</t>
-  </si>
-  <si>
-    <t>T-6024</t>
-  </si>
-  <si>
-    <t>T-6025</t>
-  </si>
-  <si>
-    <t>SP SEL_PREDICCION_EXPLICACION: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
-  </si>
-  <si>
-    <t>T-6026</t>
-  </si>
-  <si>
-    <t>T-6027</t>
-  </si>
-  <si>
-    <t>T-6028</t>
-  </si>
-  <si>
-    <t>GET /api/predicciones/{id}/explicacion — consulta con filtros y paginación.</t>
-  </si>
-  <si>
-    <t>T-6029</t>
-  </si>
-  <si>
-    <t>T-6030</t>
-  </si>
-  <si>
-    <t>Pantalla PrediccionExplicacion.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
-  </si>
-  <si>
-    <t>T-6031</t>
-  </si>
-  <si>
-    <t>T-6032</t>
-  </si>
-  <si>
-    <t>T-6033</t>
-  </si>
-  <si>
-    <t>T-6034</t>
-  </si>
-  <si>
-    <t>T-6035</t>
-  </si>
-  <si>
-    <t>Modelo: CREAR la tabla Indicador_Valor — todavía no existe. Columnas, PK, FK a sus padres y columna ind_uuid con índice UNIQUE para que la sincronización no duplique.</t>
-  </si>
-  <si>
-    <t>T-6036</t>
-  </si>
-  <si>
-    <t>SP SEL_INDICADOR_TABLERO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
-  </si>
-  <si>
-    <t>T-6037</t>
-  </si>
-  <si>
-    <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Indicador_Valor crezca.</t>
-  </si>
-  <si>
-    <t>T-6038</t>
-  </si>
-  <si>
-    <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
-  </si>
-  <si>
-    <t>T-6039</t>
-  </si>
-  <si>
-    <t>GET /api/indicador-tableros — consulta con filtros y paginación.</t>
-  </si>
-  <si>
-    <t>T-6040</t>
-  </si>
-  <si>
-    <t>T-6041</t>
-  </si>
-  <si>
-    <t>Pantalla IndicadorTablero.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
-  </si>
-  <si>
-    <t>T-6042</t>
-  </si>
-  <si>
-    <t>T-6043</t>
-  </si>
-  <si>
-    <t>T-6044</t>
-  </si>
-  <si>
-    <t>T-6045</t>
-  </si>
-  <si>
-    <t>T-6046</t>
-  </si>
-  <si>
-    <t>Modelo: revisar Alerta — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
-  </si>
-  <si>
-    <t>T-6047</t>
-  </si>
-  <si>
-    <t>SP ALERTA_PREDICCION: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
-  </si>
-  <si>
-    <t>T-6048</t>
-  </si>
-  <si>
-    <t>T-6049</t>
-  </si>
-  <si>
-    <t>SP SEL_ALERTA_PREDICCION: consultar el resultado del proceso.</t>
-  </si>
-  <si>
-    <t>T-6050</t>
-  </si>
-  <si>
-    <t>Datos de prueba en Alerta para poder ejercitar los criterios de aceptación.</t>
-  </si>
-  <si>
-    <t>T-6051</t>
-  </si>
-  <si>
-    <t>POST /api/alerta-predicciones — dispara el proceso y devuelve su resultado.</t>
-  </si>
-  <si>
-    <t>T-6052</t>
-  </si>
-  <si>
     <t>T-6053</t>
   </si>
   <si>
@@ -893,24 +875,6 @@
     <t>T-6063</t>
   </si>
   <si>
-    <t>T-6064</t>
-  </si>
-  <si>
-    <t>POST /api/prediccion-resultados — alta. Idempotente por uuid para que un reintento del teléfono no cree dos registros.</t>
-  </si>
-  <si>
-    <t>T-6065</t>
-  </si>
-  <si>
-    <t>GET /api/prediccion-resultados/{id} y GET /api/prediccion-resultados — detalle y listado.</t>
-  </si>
-  <si>
-    <t>T-6066</t>
-  </si>
-  <si>
-    <t>Mapeo DTO ↔ entidad y validación del cuerpo antes de llamar al SP.</t>
-  </si>
-  <si>
     <t>T-6067</t>
   </si>
   <si>
@@ -947,15 +911,6 @@
     <t>T-6075</t>
   </si>
   <si>
-    <t>T-6076</t>
-  </si>
-  <si>
-    <t>GET /api/indicador-cumplimientos — consulta con filtros y paginación.</t>
-  </si>
-  <si>
-    <t>T-6077</t>
-  </si>
-  <si>
     <t>T-6078</t>
   </si>
   <si>
@@ -986,15 +941,6 @@
     <t>T-6085</t>
   </si>
   <si>
-    <t>T-6086</t>
-  </si>
-  <si>
-    <t>GET /api/indicador-disponibilidades — consulta con filtros y paginación.</t>
-  </si>
-  <si>
-    <t>T-6087</t>
-  </si>
-  <si>
     <t>T-6088</t>
   </si>
   <si>
@@ -1028,15 +974,6 @@
     <t>T-6096</t>
   </si>
   <si>
-    <t>T-6097</t>
-  </si>
-  <si>
-    <t>GET /api/indicador-costos — consulta con filtros y paginación.</t>
-  </si>
-  <si>
-    <t>T-6098</t>
-  </si>
-  <si>
     <t>T-6099</t>
   </si>
   <si>
@@ -1082,15 +1019,6 @@
     <t>Datos de prueba en Importacion_Carga para poder ejercitar los criterios de aceptación.</t>
   </si>
   <si>
-    <t>T-6109</t>
-  </si>
-  <si>
-    <t>POST /api/importacion-activos — dispara el proceso y devuelve su resultado.</t>
-  </si>
-  <si>
-    <t>T-6110</t>
-  </si>
-  <si>
     <t>T-6111</t>
   </si>
   <si>
@@ -1181,15 +1109,6 @@
     <t>Datos de prueba en Importacion_Carga_Celda para poder ejercitar los criterios de aceptación.</t>
   </si>
   <si>
-    <t>T-6132</t>
-  </si>
-  <si>
-    <t>POST /api/importacion-celdas — dispara el proceso y devuelve su resultado.</t>
-  </si>
-  <si>
-    <t>T-6133</t>
-  </si>
-  <si>
     <t>T-6134</t>
   </si>
   <si>
@@ -1229,15 +1148,6 @@
     <t>T-6143</t>
   </si>
   <si>
-    <t>T-6144</t>
-  </si>
-  <si>
-    <t>POST /api/importacion-planes — dispara el proceso y devuelve su resultado.</t>
-  </si>
-  <si>
-    <t>T-6145</t>
-  </si>
-  <si>
     <t>T-6146</t>
   </si>
   <si>
@@ -1292,30 +1202,6 @@
     <t>Datos de prueba en Modelo_Predictivo para poder ejercitar los criterios de aceptación.</t>
   </si>
   <si>
-    <t>T-6157</t>
-  </si>
-  <si>
-    <t>GET /api/modelo-predictivos — listado con filtros y paginación. DTO de salida sin exponer columnas internas.</t>
-  </si>
-  <si>
-    <t>T-6158</t>
-  </si>
-  <si>
-    <t>GET /api/modelo-predictivos/{id} — detalle.</t>
-  </si>
-  <si>
-    <t>T-6159</t>
-  </si>
-  <si>
-    <t>POST /api/modelo-predictivos — alta. Valida el cuerpo y traduce el error del SP a un 400 con mensaje legible.</t>
-  </si>
-  <si>
-    <t>T-6160</t>
-  </si>
-  <si>
-    <t>PUT /api/modelo-predictivos/{id} — edición. DELETE /api/modelo-predictivos/{id} — baja lógica.</t>
-  </si>
-  <si>
     <t>T-6161</t>
   </si>
   <si>
@@ -1373,15 +1259,6 @@
     <t>Datos de prueba en Modelo_Predictivo_Version para poder ejercitar los criterios de aceptación.</t>
   </si>
   <si>
-    <t>T-6173</t>
-  </si>
-  <si>
-    <t>POST /api/modelo-versiones — dispara el proceso y devuelve su resultado.</t>
-  </si>
-  <si>
-    <t>T-6174</t>
-  </si>
-  <si>
     <t>T-6175</t>
   </si>
   <si>
@@ -1427,15 +1304,6 @@
     <t>Datos de prueba en Dataset_Entrenamiento para poder ejercitar los criterios de aceptación.</t>
   </si>
   <si>
-    <t>T-6185</t>
-  </si>
-  <si>
-    <t>POST /api/dataset-entrenamientos — dispara el proceso y devuelve su resultado.</t>
-  </si>
-  <si>
-    <t>T-6186</t>
-  </si>
-  <si>
     <t>T-6187</t>
   </si>
   <si>
@@ -1475,15 +1343,6 @@
     <t>T-6196</t>
   </si>
   <si>
-    <t>T-6197</t>
-  </si>
-  <si>
-    <t>POST /api/indicadores/exportar — dispara el proceso y devuelve su resultado.</t>
-  </si>
-  <si>
-    <t>T-6198</t>
-  </si>
-  <si>
     <t>T-6199</t>
   </si>
   <si>
@@ -1523,15 +1382,6 @@
     <t>Datos de prueba en Analisis_Visual_Deteccion para poder ejercitar los criterios de aceptación.</t>
   </si>
   <si>
-    <t>T-6207</t>
-  </si>
-  <si>
-    <t>GET /api/analisis-visual-detecciones — consulta con filtros y paginación.</t>
-  </si>
-  <si>
-    <t>T-6208</t>
-  </si>
-  <si>
     <t>T-6209</t>
   </si>
   <si>
@@ -1574,15 +1424,6 @@
     <t>Datos de prueba en Modelo_Monitoreo para poder ejercitar los criterios de aceptación.</t>
   </si>
   <si>
-    <t>T-6218</t>
-  </si>
-  <si>
-    <t>GET /api/modelo-monitoreos — consulta con filtros y paginación.</t>
-  </si>
-  <si>
-    <t>T-6219</t>
-  </si>
-  <si>
     <t>T-6220</t>
   </si>
   <si>
@@ -1617,15 +1458,6 @@
   </si>
   <si>
     <t>T-6228</t>
-  </si>
-  <si>
-    <t>T-6229</t>
-  </si>
-  <si>
-    <t>GET /api/importaciones/historial — consulta con filtros y paginación.</t>
-  </si>
-  <si>
-    <t>T-6230</t>
   </si>
   <si>
     <t>T-6231</t>
@@ -3232,8 +3064,8 @@
         <v>29</v>
       </c>
       <c r="C32" s="8">
-        <f>SUM(Tareas!$F$6:$F$239)</f>
-        <v>220.5</v>
+        <f>SUM(Tareas!$F$6:$F$204)</f>
+        <v>179.25</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3242,7 +3074,7 @@
       </c>
       <c r="C33" s="9">
         <f>IFERROR($C$32/$C$29,0)</f>
-        <v>0.91874999999999996</v>
+        <v>0.74687499999999996</v>
       </c>
     </row>
     <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3251,7 +3083,7 @@
       </c>
       <c r="C34" s="8">
         <f>$C$29-$C$32</f>
-        <v>19.5</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3360,10 +3192,10 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B11:H13"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C16:H16"/>
     <mergeCell ref="C21:H21"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C19:H19"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="B43:H44"/>
     <mergeCell ref="C23:H23"/>
@@ -3536,7 +3368,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A6,Tareas!$F$6:$F$239)</f>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A6,Tareas!$F$6:$F$204)</f>
         <v>12</v>
       </c>
       <c r="N6" s="11" t="s">
@@ -3583,8 +3415,8 @@
         <v>4</v>
       </c>
       <c r="M7" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A7,Tareas!$F$6:$F$239)</f>
-        <v>7.5</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A7,Tareas!$F$6:$F$204)</f>
+        <v>5.75</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>71</v>
@@ -3630,7 +3462,7 @@
         <v>4</v>
       </c>
       <c r="M8" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A8,Tareas!$F$6:$F$239)</f>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A8,Tareas!$F$6:$F$204)</f>
         <v>7.5</v>
       </c>
       <c r="N8" s="11" t="s">
@@ -3677,8 +3509,8 @@
         <v>3</v>
       </c>
       <c r="M9" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A9,Tareas!$F$6:$F$239)</f>
-        <v>12</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A9,Tareas!$F$6:$F$204)</f>
+        <v>9.25</v>
       </c>
       <c r="N9" s="13" t="s">
         <v>71</v>
@@ -3724,7 +3556,7 @@
         <v>7</v>
       </c>
       <c r="M10" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A10,Tareas!$F$6:$F$239)</f>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A10,Tareas!$F$6:$F$204)</f>
         <v>12</v>
       </c>
       <c r="N10" s="11" t="s">
@@ -3771,8 +3603,8 @@
         <v>3</v>
       </c>
       <c r="M11" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A11,Tareas!$F$6:$F$239)</f>
-        <v>7.5</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A11,Tareas!$F$6:$F$204)</f>
+        <v>5.75</v>
       </c>
       <c r="N11" s="13" t="s">
         <v>71</v>
@@ -3818,8 +3650,8 @@
         <v>3</v>
       </c>
       <c r="M12" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A12,Tareas!$F$6:$F$239)</f>
-        <v>7.5</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A12,Tareas!$F$6:$F$204)</f>
+        <v>5.75</v>
       </c>
       <c r="N12" s="11" t="s">
         <v>71</v>
@@ -3865,8 +3697,8 @@
         <v>3</v>
       </c>
       <c r="M13" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A13,Tareas!$F$6:$F$239)</f>
-        <v>12</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A13,Tareas!$F$6:$F$204)</f>
+        <v>9.25</v>
       </c>
       <c r="N13" s="13" t="s">
         <v>71</v>
@@ -3912,8 +3744,8 @@
         <v>3</v>
       </c>
       <c r="M14" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A14,Tareas!$F$6:$F$239)</f>
-        <v>12</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A14,Tareas!$F$6:$F$204)</f>
+        <v>9.25</v>
       </c>
       <c r="N14" s="11" t="s">
         <v>71</v>
@@ -3959,8 +3791,8 @@
         <v>4</v>
       </c>
       <c r="M15" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A15,Tareas!$F$6:$F$239)</f>
-        <v>19.5</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A15,Tareas!$F$6:$F$204)</f>
+        <v>15.25</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>71</v>
@@ -4006,7 +3838,7 @@
         <v>3</v>
       </c>
       <c r="M16" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A16,Tareas!$F$6:$F$239)</f>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A16,Tareas!$F$6:$F$204)</f>
         <v>7.5</v>
       </c>
       <c r="N16" s="11" t="s">
@@ -4053,8 +3885,8 @@
         <v>4</v>
       </c>
       <c r="M17" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A17,Tareas!$F$6:$F$239)</f>
-        <v>12</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A17,Tareas!$F$6:$F$204)</f>
+        <v>9.25</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>71</v>
@@ -4100,8 +3932,8 @@
         <v>3</v>
       </c>
       <c r="M18" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A18,Tareas!$F$6:$F$239)</f>
-        <v>19.5</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A18,Tareas!$F$6:$F$204)</f>
+        <v>15.25</v>
       </c>
       <c r="N18" s="11" t="s">
         <v>71</v>
@@ -4147,8 +3979,8 @@
         <v>3</v>
       </c>
       <c r="M19" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A19,Tareas!$F$6:$F$239)</f>
-        <v>12</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A19,Tareas!$F$6:$F$204)</f>
+        <v>9.25</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>71</v>
@@ -4194,8 +4026,8 @@
         <v>3</v>
       </c>
       <c r="M20" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A20,Tareas!$F$6:$F$239)</f>
-        <v>12</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A20,Tareas!$F$6:$F$204)</f>
+        <v>9.25</v>
       </c>
       <c r="N20" s="11" t="s">
         <v>71</v>
@@ -4241,8 +4073,8 @@
         <v>3</v>
       </c>
       <c r="M21" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A21,Tareas!$F$6:$F$239)</f>
-        <v>12</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A21,Tareas!$F$6:$F$204)</f>
+        <v>9.25</v>
       </c>
       <c r="N21" s="13" t="s">
         <v>71</v>
@@ -4288,8 +4120,8 @@
         <v>2</v>
       </c>
       <c r="M22" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A22,Tareas!$F$6:$F$239)</f>
-        <v>7.5</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A22,Tareas!$F$6:$F$204)</f>
+        <v>5.75</v>
       </c>
       <c r="N22" s="11" t="s">
         <v>71</v>
@@ -4335,8 +4167,8 @@
         <v>4</v>
       </c>
       <c r="M23" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A23,Tareas!$F$6:$F$239)</f>
-        <v>12</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A23,Tareas!$F$6:$F$204)</f>
+        <v>9.25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>71</v>
@@ -4382,8 +4214,8 @@
         <v>3</v>
       </c>
       <c r="M24" s="11">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A24,Tareas!$F$6:$F$239)</f>
-        <v>12</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A24,Tareas!$F$6:$F$204)</f>
+        <v>9.25</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>71</v>
@@ -4429,8 +4261,8 @@
         <v>2</v>
       </c>
       <c r="M25" s="13">
-        <f>SUMIF(Tareas!$B$6:$B$239,$A25,Tareas!$F$6:$F$239)</f>
-        <v>4.5</v>
+        <f>SUMIF(Tareas!$B$6:$B$204,$A25,Tareas!$F$6:$F$204)</f>
+        <v>3.5</v>
       </c>
       <c r="N25" s="13" t="s">
         <v>71</v>
@@ -4461,7 +4293,7 @@
       </c>
       <c r="M26" s="15">
         <f>SUM(M6:M25)</f>
-        <v>220.5</v>
+        <v>179.25</v>
       </c>
       <c r="N26" s="15"/>
       <c r="O26" s="16"/>
@@ -4491,13 +4323,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="N6:N25" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Estado no valido" error="Estados: Por hacer, En curso, En revisión, Terminada o Bloqueada." sqref="N6:N25" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Por hacer,En curso,En revisión,Terminada,Bloqueada"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="O6:O25" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Responsable no valido" error="Elige a alguien del equipo: Bryan Chávez, Catalina Pescio o Emilio Fuentes." sqref="O6:O25" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Bryan Chávez,Catalina Pescio,Emilio Fuentes"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
@@ -5078,13 +4908,13 @@
         <v>216</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="F23" s="11">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>71</v>
@@ -5103,13 +4933,13 @@
         <v>73</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F24" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>17</v>
@@ -5122,7 +4952,7 @@
     </row>
     <row r="25" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>72</v>
@@ -5131,16 +4961,16 @@
         <v>73</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F25" s="11">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>71</v>
@@ -5150,7 +4980,7 @@
     </row>
     <row r="26" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>72</v>
@@ -5159,16 +4989,16 @@
         <v>73</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F26" s="11">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H26" s="11" t="s">
         <v>71</v>
@@ -5178,25 +5008,25 @@
     </row>
     <row r="27" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F27" s="11">
         <v>0.75</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H27" s="11" t="s">
         <v>71</v>
@@ -5206,25 +5036,25 @@
     </row>
     <row r="28" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="F28" s="11">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H28" s="11" t="s">
         <v>71</v>
@@ -5234,7 +5064,7 @@
     </row>
     <row r="29" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>79</v>
@@ -5243,16 +5073,16 @@
         <v>80</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F29" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>71</v>
@@ -5262,7 +5092,7 @@
     </row>
     <row r="30" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>79</v>
@@ -5271,16 +5101,16 @@
         <v>80</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>226</v>
+        <v>182</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F30" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>71</v>
@@ -5290,7 +5120,7 @@
     </row>
     <row r="31" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>79</v>
@@ -5299,16 +5129,16 @@
         <v>80</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>180</v>
+        <v>226</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F31" s="11">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>71</v>
@@ -5318,7 +5148,7 @@
     </row>
     <row r="32" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>79</v>
@@ -5327,16 +5157,16 @@
         <v>80</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F32" s="11">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>71</v>
@@ -5346,7 +5176,7 @@
     </row>
     <row r="33" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>79</v>
@@ -5355,13 +5185,13 @@
         <v>80</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="F33" s="11">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>19</v>
@@ -5374,7 +5204,7 @@
     </row>
     <row r="34" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>79</v>
@@ -5383,10 +5213,10 @@
         <v>80</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F34" s="11">
         <v>0.75</v>
@@ -5402,7 +5232,7 @@
     </row>
     <row r="35" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>79</v>
@@ -5411,13 +5241,13 @@
         <v>80</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="F35" s="11">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>19</v>
@@ -5428,9 +5258,9 @@
       <c r="I35" s="11"/>
       <c r="J35" s="12"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>79</v>
@@ -5439,16 +5269,16 @@
         <v>80</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F36" s="11">
         <v>0.75</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>71</v>
@@ -5458,7 +5288,7 @@
     </row>
     <row r="37" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>79</v>
@@ -5467,16 +5297,16 @@
         <v>80</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F37" s="11">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H37" s="11" t="s">
         <v>71</v>
@@ -5486,25 +5316,25 @@
     </row>
     <row r="38" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F38" s="11">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H38" s="11" t="s">
         <v>71</v>
@@ -5514,22 +5344,22 @@
     </row>
     <row r="39" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="B39" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>200</v>
-      </c>
       <c r="E39" s="11" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="F39" s="11">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>15</v>
@@ -5560,7 +5390,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H40" s="11" t="s">
         <v>71</v>
@@ -5585,10 +5415,10 @@
         <v>176</v>
       </c>
       <c r="F41" s="11">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H41" s="11" t="s">
         <v>71</v>
@@ -5610,13 +5440,13 @@
         <v>243</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="F42" s="11">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H42" s="11" t="s">
         <v>71</v>
@@ -5635,13 +5465,13 @@
         <v>85</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="F43" s="11">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G43" s="12" t="s">
         <v>17</v>
@@ -5654,7 +5484,7 @@
     </row>
     <row r="44" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>84</v>
@@ -5663,16 +5493,16 @@
         <v>85</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>247</v>
+        <v>197</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F44" s="11">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>71</v>
@@ -5682,7 +5512,7 @@
     </row>
     <row r="45" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>84</v>
@@ -5691,16 +5521,16 @@
         <v>85</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="F45" s="11">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H45" s="11" t="s">
         <v>71</v>
@@ -5710,7 +5540,7 @@
     </row>
     <row r="46" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>84</v>
@@ -5719,16 +5549,16 @@
         <v>85</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>250</v>
+        <v>203</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="F46" s="11">
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H46" s="11" t="s">
         <v>71</v>
@@ -5738,25 +5568,25 @@
     </row>
     <row r="47" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="F47" s="11">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H47" s="11" t="s">
         <v>71</v>
@@ -5766,25 +5596,25 @@
     </row>
     <row r="48" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>197</v>
+        <v>251</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F48" s="11">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H48" s="11" t="s">
         <v>71</v>
@@ -5794,25 +5624,25 @@
     </row>
     <row r="49" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="F49" s="11">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H49" s="11" t="s">
         <v>71</v>
@@ -5822,22 +5652,22 @@
     </row>
     <row r="50" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="B50" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D50" s="17" t="s">
-        <v>203</v>
-      </c>
       <c r="E50" s="11" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="F50" s="11">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>15</v>
@@ -5868,7 +5698,7 @@
         <v>0.75</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H51" s="11" t="s">
         <v>71</v>
@@ -5890,10 +5720,10 @@
         <v>258</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F52" s="11">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>19</v>
@@ -5915,13 +5745,13 @@
         <v>90</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F53" s="11">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>17</v>
@@ -5934,7 +5764,7 @@
     </row>
     <row r="54" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>89</v>
@@ -5943,16 +5773,16 @@
         <v>90</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="F54" s="11">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H54" s="11" t="s">
         <v>71</v>
@@ -5962,7 +5792,7 @@
     </row>
     <row r="55" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>89</v>
@@ -5971,13 +5801,13 @@
         <v>90</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>263</v>
+        <v>191</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="F55" s="11">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G55" s="12" t="s">
         <v>19</v>
@@ -5999,13 +5829,13 @@
         <v>90</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>265</v>
+        <v>194</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F56" s="11">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G56" s="12" t="s">
         <v>19</v>
@@ -6018,7 +5848,7 @@
     </row>
     <row r="57" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>89</v>
@@ -6027,16 +5857,16 @@
         <v>90</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F57" s="11">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H57" s="11" t="s">
         <v>71</v>
@@ -6046,7 +5876,7 @@
     </row>
     <row r="58" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>89</v>
@@ -6055,16 +5885,16 @@
         <v>90</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>268</v>
+        <v>200</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="F58" s="11">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H58" s="11" t="s">
         <v>71</v>
@@ -6072,9 +5902,9 @@
       <c r="I58" s="11"/>
       <c r="J58" s="12"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>89</v>
@@ -6083,16 +5913,16 @@
         <v>90</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F59" s="11">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H59" s="11" t="s">
         <v>71</v>
@@ -6102,25 +5932,25 @@
     </row>
     <row r="60" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="F60" s="11">
         <v>0.75</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H60" s="11" t="s">
         <v>71</v>
@@ -6130,22 +5960,22 @@
     </row>
     <row r="61" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="11" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>197</v>
+        <v>270</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F61" s="11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G61" s="12" t="s">
         <v>15</v>
@@ -6158,25 +5988,25 @@
     </row>
     <row r="62" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D62" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="B62" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>200</v>
-      </c>
       <c r="E62" s="11" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="F62" s="11">
         <v>0.5</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H62" s="11" t="s">
         <v>71</v>
@@ -6189,22 +6019,22 @@
         <v>273</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>203</v>
+        <v>274</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="F63" s="11">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H63" s="11" t="s">
         <v>71</v>
@@ -6214,7 +6044,7 @@
     </row>
     <row r="64" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>94</v>
@@ -6223,16 +6053,16 @@
         <v>95</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F64" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H64" s="11" t="s">
         <v>71</v>
@@ -6242,7 +6072,7 @@
     </row>
     <row r="65" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>94</v>
@@ -6251,16 +6081,16 @@
         <v>95</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="F65" s="11">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H65" s="11" t="s">
         <v>71</v>
@@ -6270,7 +6100,7 @@
     </row>
     <row r="66" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>94</v>
@@ -6279,13 +6109,13 @@
         <v>95</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="F66" s="11">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>19</v>
@@ -6298,7 +6128,7 @@
     </row>
     <row r="67" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>94</v>
@@ -6307,10 +6137,10 @@
         <v>95</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>280</v>
+        <v>194</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="F67" s="11">
         <v>0.5</v>
@@ -6335,13 +6165,13 @@
         <v>95</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="F68" s="11">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G68" s="12" t="s">
         <v>15</v>
@@ -6363,16 +6193,16 @@
         <v>95</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="F69" s="11">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="G69" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H69" s="11" t="s">
         <v>71</v>
@@ -6382,25 +6212,25 @@
     </row>
     <row r="70" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>285</v>
+        <v>235</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F70" s="11">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H70" s="11" t="s">
         <v>71</v>
@@ -6410,25 +6240,25 @@
     </row>
     <row r="71" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F71" s="11">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H71" s="11" t="s">
         <v>71</v>
@@ -6438,25 +6268,25 @@
     </row>
     <row r="72" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="11" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>289</v>
+        <v>239</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="F72" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H72" s="11" t="s">
         <v>71</v>
@@ -6466,22 +6296,22 @@
     </row>
     <row r="73" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>291</v>
+        <v>241</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="F73" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G73" s="12" t="s">
         <v>19</v>
@@ -6494,22 +6324,22 @@
     </row>
     <row r="74" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="11" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>194</v>
+        <v>289</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="F74" s="11">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G74" s="12" t="s">
         <v>17</v>
@@ -6522,25 +6352,25 @@
     </row>
     <row r="75" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="11" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F75" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H75" s="11" t="s">
         <v>71</v>
@@ -6550,22 +6380,22 @@
     </row>
     <row r="76" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F76" s="11">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G76" s="12" t="s">
         <v>15</v>
@@ -6578,7 +6408,7 @@
     </row>
     <row r="77" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="11" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B77" s="11" t="s">
         <v>98</v>
@@ -6587,16 +6417,16 @@
         <v>99</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="F77" s="11">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H77" s="11" t="s">
         <v>71</v>
@@ -6606,22 +6436,22 @@
     </row>
     <row r="78" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>297</v>
+        <v>235</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F78" s="11">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>17</v>
@@ -6634,22 +6464,22 @@
     </row>
     <row r="79" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>243</v>
+        <v>295</v>
       </c>
       <c r="E79" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F79" s="11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G79" s="12" t="s">
         <v>15</v>
@@ -6662,22 +6492,22 @@
     </row>
     <row r="80" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E80" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F80" s="11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G80" s="12" t="s">
         <v>19</v>
@@ -6690,22 +6520,22 @@
     </row>
     <row r="81" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>301</v>
+        <v>241</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F81" s="11">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>17</v>
@@ -6718,22 +6548,22 @@
     </row>
     <row r="82" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>187</v>
+        <v>299</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="F82" s="11">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>19</v>
@@ -6746,22 +6576,22 @@
     </row>
     <row r="83" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>304</v>
+        <v>194</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="F83" s="11">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>17</v>
@@ -6774,25 +6604,25 @@
     </row>
     <row r="84" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F84" s="11">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H84" s="11" t="s">
         <v>71</v>
@@ -6802,22 +6632,22 @@
     </row>
     <row r="85" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F85" s="11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G85" s="12" t="s">
         <v>15</v>
@@ -6830,19 +6660,19 @@
     </row>
     <row r="86" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F86" s="11">
         <v>0.25</v>
@@ -6858,16 +6688,16 @@
     </row>
     <row r="87" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="11" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E87" s="11" t="s">
         <v>176</v>
@@ -6876,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H87" s="11" t="s">
         <v>71</v>
@@ -6886,16 +6716,16 @@
     </row>
     <row r="88" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E88" s="11" t="s">
         <v>176</v>
@@ -6904,7 +6734,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H88" s="11" t="s">
         <v>71</v>
@@ -6914,16 +6744,16 @@
     </row>
     <row r="89" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="11" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>176</v>
@@ -6932,7 +6762,7 @@
         <v>1</v>
       </c>
       <c r="G89" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H89" s="11" t="s">
         <v>71</v>
@@ -6942,16 +6772,16 @@
     </row>
     <row r="90" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="11" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E90" s="11" t="s">
         <v>176</v>
@@ -6960,7 +6790,7 @@
         <v>0.75</v>
       </c>
       <c r="G90" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H90" s="11" t="s">
         <v>71</v>
@@ -6970,22 +6800,22 @@
     </row>
     <row r="91" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="11" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="F91" s="11">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G91" s="12" t="s">
         <v>17</v>
@@ -6998,22 +6828,22 @@
     </row>
     <row r="92" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="11" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F92" s="11">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G92" s="12" t="s">
         <v>19</v>
@@ -7026,25 +6856,25 @@
     </row>
     <row r="93" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="11" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>317</v>
+        <v>197</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F93" s="11">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H93" s="11" t="s">
         <v>71</v>
@@ -7054,25 +6884,25 @@
     </row>
     <row r="94" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="11" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F94" s="11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G94" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H94" s="11" t="s">
         <v>71</v>
@@ -7082,22 +6912,22 @@
     </row>
     <row r="95" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="11" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F95" s="11">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>15</v>
@@ -7110,25 +6940,25 @@
     </row>
     <row r="96" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="11" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>200</v>
+        <v>316</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="F96" s="11">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="G96" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H96" s="11" t="s">
         <v>71</v>
@@ -7138,25 +6968,25 @@
     </row>
     <row r="97" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>203</v>
+        <v>318</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="F97" s="11">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="G97" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H97" s="11" t="s">
         <v>71</v>
@@ -7166,22 +6996,22 @@
     </row>
     <row r="98" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="11" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="E98" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F98" s="11">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G98" s="12" t="s">
         <v>15</v>
@@ -7194,22 +7024,22 @@
     </row>
     <row r="99" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E99" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F99" s="11">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G99" s="12" t="s">
         <v>19</v>
@@ -7222,22 +7052,22 @@
     </row>
     <row r="100" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>243</v>
+        <v>323</v>
       </c>
       <c r="E100" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F100" s="11">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G100" s="12" t="s">
         <v>17</v>
@@ -7250,25 +7080,25 @@
     </row>
     <row r="101" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="11" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D101" s="17" t="s">
-        <v>245</v>
+        <v>325</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="F101" s="11">
-        <v>0.75</v>
+        <v>4</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H101" s="11" t="s">
         <v>71</v>
@@ -7278,19 +7108,19 @@
     </row>
     <row r="102" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>328</v>
+        <v>194</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F102" s="11">
         <v>1.5</v>
@@ -7306,25 +7136,25 @@
     </row>
     <row r="103" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="11" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D103" s="17" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F103" s="11">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="G103" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H103" s="11" t="s">
         <v>71</v>
@@ -7334,25 +7164,25 @@
     </row>
     <row r="104" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>331</v>
+        <v>200</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="F104" s="11">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G104" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H104" s="11" t="s">
         <v>71</v>
@@ -7362,25 +7192,25 @@
     </row>
     <row r="105" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="11" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="F105" s="11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G105" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H105" s="11" t="s">
         <v>71</v>
@@ -7390,22 +7220,22 @@
     </row>
     <row r="106" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F106" s="11">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G106" s="12" t="s">
         <v>15</v>
@@ -7418,25 +7248,25 @@
     </row>
     <row r="107" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="11" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>200</v>
+        <v>332</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="F107" s="11">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G107" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H107" s="11" t="s">
         <v>71</v>
@@ -7446,25 +7276,25 @@
     </row>
     <row r="108" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="11" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>203</v>
+        <v>334</v>
       </c>
       <c r="E108" s="11" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="F108" s="11">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G108" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H108" s="11" t="s">
         <v>71</v>
@@ -7474,25 +7304,25 @@
     </row>
     <row r="109" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>337</v>
+        <v>256</v>
       </c>
       <c r="E109" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F109" s="11">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="G109" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H109" s="11" t="s">
         <v>71</v>
@@ -7502,22 +7332,22 @@
     </row>
     <row r="110" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="11" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F110" s="11">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G110" s="12" t="s">
         <v>17</v>
@@ -7530,25 +7360,25 @@
     </row>
     <row r="111" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F111" s="11">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G111" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H111" s="11" t="s">
         <v>71</v>
@@ -7558,25 +7388,25 @@
     </row>
     <row r="112" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="11" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="F112" s="11">
         <v>1.25</v>
       </c>
       <c r="G112" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H112" s="11" t="s">
         <v>71</v>
@@ -7586,22 +7416,22 @@
     </row>
     <row r="113" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="11" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>344</v>
+        <v>191</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="F113" s="11">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G113" s="12" t="s">
         <v>17</v>
@@ -7614,25 +7444,25 @@
     </row>
     <row r="114" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="11" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>346</v>
+        <v>194</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F114" s="11">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H114" s="11" t="s">
         <v>71</v>
@@ -7642,25 +7472,25 @@
     </row>
     <row r="115" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="11" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F115" s="11">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="G115" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H115" s="11" t="s">
         <v>71</v>
@@ -7670,25 +7500,25 @@
     </row>
     <row r="116" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="11" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>349</v>
+        <v>200</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="F116" s="11">
-        <v>4</v>
+        <v>0.25</v>
       </c>
       <c r="G116" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H116" s="11" t="s">
         <v>71</v>
@@ -7698,25 +7528,25 @@
     </row>
     <row r="117" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="11" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>194</v>
+        <v>346</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="F117" s="11">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G117" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H117" s="11" t="s">
         <v>71</v>
@@ -7726,25 +7556,25 @@
     </row>
     <row r="118" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>197</v>
+        <v>348</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F118" s="11">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="G118" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H118" s="11" t="s">
         <v>71</v>
@@ -7754,19 +7584,19 @@
     </row>
     <row r="119" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="11" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="F119" s="11">
         <v>0.75</v>
@@ -7782,25 +7612,25 @@
     </row>
     <row r="120" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="11" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>203</v>
+        <v>351</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="F120" s="11">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G120" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H120" s="11" t="s">
         <v>71</v>
@@ -7810,16 +7640,16 @@
     </row>
     <row r="121" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="11" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>256</v>
+        <v>353</v>
       </c>
       <c r="E121" s="11" t="s">
         <v>176</v>
@@ -7828,7 +7658,7 @@
         <v>0.75</v>
       </c>
       <c r="G121" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H121" s="11" t="s">
         <v>71</v>
@@ -7838,22 +7668,22 @@
     </row>
     <row r="122" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="B122" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D122" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="B122" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C122" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D122" s="17" t="s">
-        <v>356</v>
-      </c>
       <c r="E122" s="11" t="s">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="F122" s="11">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
       <c r="G122" s="12" t="s">
         <v>19</v>
@@ -7866,22 +7696,22 @@
     </row>
     <row r="123" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>358</v>
+        <v>194</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="F123" s="11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>17</v>
@@ -7894,22 +7724,22 @@
     </row>
     <row r="124" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="11" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D124" s="17" t="s">
-        <v>263</v>
+        <v>197</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="F124" s="11">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="G124" s="12" t="s">
         <v>15</v>
@@ -7920,27 +7750,27 @@
       <c r="I124" s="11"/>
       <c r="J124" s="12"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="11" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D125" s="17" t="s">
-        <v>361</v>
+        <v>200</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="F125" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G125" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H125" s="11" t="s">
         <v>71</v>
@@ -7950,25 +7780,25 @@
     </row>
     <row r="126" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D126" s="17" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="F126" s="11">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="G126" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H126" s="11" t="s">
         <v>71</v>
@@ -7978,25 +7808,25 @@
     </row>
     <row r="127" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="11" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>364</v>
+        <v>316</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="F127" s="11">
         <v>1.25</v>
       </c>
       <c r="G127" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H127" s="11" t="s">
         <v>71</v>
@@ -8004,27 +7834,27 @@
       <c r="I127" s="11"/>
       <c r="J127" s="12"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="11" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>191</v>
+        <v>362</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F128" s="11">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="G128" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H128" s="11" t="s">
         <v>71</v>
@@ -8034,25 +7864,25 @@
     </row>
     <row r="129" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="11" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D129" s="17" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="E129" s="11" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="F129" s="11">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="G129" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H129" s="11" t="s">
         <v>71</v>
@@ -8062,22 +7892,22 @@
     </row>
     <row r="130" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="11" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D130" s="17" t="s">
-        <v>197</v>
+        <v>365</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F130" s="11">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="G130" s="12" t="s">
         <v>15</v>
@@ -8090,25 +7920,25 @@
     </row>
     <row r="131" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="11" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D131" s="17" t="s">
-        <v>200</v>
+        <v>323</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="F131" s="11">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="G131" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H131" s="11" t="s">
         <v>71</v>
@@ -8118,25 +7948,25 @@
     </row>
     <row r="132" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="11" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="F132" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G132" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H132" s="11" t="s">
         <v>71</v>
@@ -8146,25 +7976,25 @@
     </row>
     <row r="133" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="11" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D133" s="17" t="s">
-        <v>372</v>
+        <v>194</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="F133" s="11">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G133" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H133" s="11" t="s">
         <v>71</v>
@@ -8174,22 +8004,22 @@
     </row>
     <row r="134" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="11" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D134" s="17" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="F134" s="11">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
       <c r="G134" s="12" t="s">
         <v>15</v>
@@ -8202,25 +8032,25 @@
     </row>
     <row r="135" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="11" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="F135" s="11">
         <v>0.75</v>
       </c>
       <c r="G135" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H135" s="11" t="s">
         <v>71</v>
@@ -8230,25 +8060,25 @@
     </row>
     <row r="136" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="11" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>377</v>
+        <v>203</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="F136" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G136" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H136" s="11" t="s">
         <v>71</v>
@@ -8258,22 +8088,22 @@
     </row>
     <row r="137" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="11" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F137" s="11">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>17</v>
@@ -8286,25 +8116,25 @@
     </row>
     <row r="138" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="11" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>218</v>
+        <v>376</v>
       </c>
       <c r="E138" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F138" s="11">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G138" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H138" s="11" t="s">
         <v>71</v>
@@ -8314,22 +8144,22 @@
     </row>
     <row r="139" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="11" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E139" s="11" t="s">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="F139" s="11">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="G139" s="12" t="s">
         <v>19</v>
@@ -8342,22 +8172,22 @@
     </row>
     <row r="140" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="11" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>194</v>
+        <v>380</v>
       </c>
       <c r="E140" s="11" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="F140" s="11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G140" s="12" t="s">
         <v>17</v>
@@ -8370,22 +8200,22 @@
     </row>
     <row r="141" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="11" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>197</v>
+        <v>382</v>
       </c>
       <c r="E141" s="11" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F141" s="11">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="G141" s="12" t="s">
         <v>15</v>
@@ -8398,25 +8228,25 @@
     </row>
     <row r="142" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="11" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>200</v>
+        <v>384</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="F142" s="11">
         <v>0.5</v>
       </c>
       <c r="G142" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H142" s="11" t="s">
         <v>71</v>
@@ -8426,25 +8256,25 @@
     </row>
     <row r="143" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="B143" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D143" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="B143" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C143" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="D143" s="17" t="s">
-        <v>203</v>
-      </c>
       <c r="E143" s="11" t="s">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="F143" s="11">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G143" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H143" s="11" t="s">
         <v>71</v>
@@ -8457,22 +8287,22 @@
         <v>387</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>337</v>
+        <v>388</v>
       </c>
       <c r="E144" s="11" t="s">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="F144" s="11">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G144" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H144" s="11" t="s">
         <v>71</v>
@@ -8482,22 +8312,22 @@
     </row>
     <row r="145" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E145" s="11" t="s">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="F145" s="11">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G145" s="12" t="s">
         <v>19</v>
@@ -8510,22 +8340,22 @@
     </row>
     <row r="146" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="E146" s="11" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="F146" s="11">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G146" s="12" t="s">
         <v>17</v>
@@ -8538,19 +8368,19 @@
     </row>
     <row r="147" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>392</v>
+        <v>197</v>
       </c>
       <c r="E147" s="11" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="F147" s="11">
         <v>1.25</v>
@@ -8569,22 +8399,22 @@
         <v>393</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>344</v>
+        <v>200</v>
       </c>
       <c r="E148" s="11" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="F148" s="11">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="G148" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H148" s="11" t="s">
         <v>71</v>
@@ -8597,22 +8427,22 @@
         <v>394</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>395</v>
+        <v>203</v>
       </c>
       <c r="E149" s="11" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="F149" s="11">
-        <v>2.25</v>
+        <v>0.25</v>
       </c>
       <c r="G149" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H149" s="11" t="s">
         <v>71</v>
@@ -8622,25 +8452,25 @@
     </row>
     <row r="150" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="B150" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D150" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="B150" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C150" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D150" s="17" t="s">
-        <v>218</v>
-      </c>
       <c r="E150" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F150" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G150" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H150" s="11" t="s">
         <v>71</v>
@@ -8653,22 +8483,22 @@
         <v>397</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D151" s="17" t="s">
         <v>398</v>
       </c>
       <c r="E151" s="11" t="s">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="F151" s="11">
-        <v>4</v>
+        <v>0.75</v>
       </c>
       <c r="G151" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H151" s="11" t="s">
         <v>71</v>
@@ -8681,19 +8511,19 @@
         <v>399</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="E152" s="11" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="F152" s="11">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="G152" s="12" t="s">
         <v>19</v>
@@ -8709,22 +8539,22 @@
         <v>400</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D153" s="17" t="s">
-        <v>197</v>
+        <v>401</v>
       </c>
       <c r="E153" s="11" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F153" s="11">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="G153" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H153" s="11" t="s">
         <v>71</v>
@@ -8734,19 +8564,19 @@
     </row>
     <row r="154" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="E154" s="11" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="F154" s="11">
         <v>0.75</v>
@@ -8762,25 +8592,25 @@
     </row>
     <row r="155" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="11" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>203</v>
+        <v>405</v>
       </c>
       <c r="E155" s="11" t="s">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="F155" s="11">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="G155" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H155" s="11" t="s">
         <v>71</v>
@@ -8790,25 +8620,25 @@
     </row>
     <row r="156" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="11" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D156" s="17" t="s">
-        <v>404</v>
+        <v>194</v>
       </c>
       <c r="E156" s="11" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="F156" s="11">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G156" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H156" s="11" t="s">
         <v>71</v>
@@ -8818,22 +8648,22 @@
     </row>
     <row r="157" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="11" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D157" s="17" t="s">
-        <v>406</v>
+        <v>197</v>
       </c>
       <c r="E157" s="11" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="F157" s="11">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="G157" s="12" t="s">
         <v>15</v>
@@ -8846,25 +8676,25 @@
     </row>
     <row r="158" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>408</v>
+        <v>200</v>
       </c>
       <c r="E158" s="11" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="F158" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G158" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H158" s="11" t="s">
         <v>71</v>
@@ -8877,22 +8707,22 @@
         <v>409</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D159" s="17" t="s">
-        <v>410</v>
+        <v>203</v>
       </c>
       <c r="E159" s="11" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="F159" s="11">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G159" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H159" s="11" t="s">
         <v>71</v>
@@ -8902,25 +8732,25 @@
     </row>
     <row r="160" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D160" s="17" t="s">
         <v>411</v>
-      </c>
-      <c r="B160" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C160" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="D160" s="17" t="s">
-        <v>412</v>
       </c>
       <c r="E160" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F160" s="11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H160" s="11" t="s">
         <v>71</v>
@@ -8930,25 +8760,25 @@
     </row>
     <row r="161" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D161" s="17" t="s">
         <v>413</v>
-      </c>
-      <c r="B161" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C161" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="D161" s="17" t="s">
-        <v>414</v>
       </c>
       <c r="E161" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F161" s="11">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G161" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H161" s="11" t="s">
         <v>71</v>
@@ -8958,25 +8788,25 @@
     </row>
     <row r="162" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="11" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D162" s="17" t="s">
-        <v>416</v>
+        <v>210</v>
       </c>
       <c r="E162" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F162" s="11">
         <v>0.75</v>
       </c>
       <c r="G162" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H162" s="11" t="s">
         <v>71</v>
@@ -8986,19 +8816,19 @@
     </row>
     <row r="163" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C163" s="12" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D163" s="17" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E163" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F163" s="11">
         <v>0.75</v>
@@ -9014,19 +8844,19 @@
     </row>
     <row r="164" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="11" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D164" s="17" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E164" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F164" s="11">
         <v>0.75</v>
@@ -9042,22 +8872,22 @@
     </row>
     <row r="165" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="11" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B165" s="11" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C165" s="12" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D165" s="17" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E165" s="11" t="s">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="F165" s="11">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>19</v>
@@ -9070,25 +8900,25 @@
     </row>
     <row r="166" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="11" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C166" s="12" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D166" s="17" t="s">
-        <v>424</v>
+        <v>194</v>
       </c>
       <c r="E166" s="11" t="s">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="F166" s="11">
         <v>1</v>
       </c>
       <c r="G166" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H166" s="11" t="s">
         <v>71</v>
@@ -9098,25 +8928,25 @@
     </row>
     <row r="167" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B167" s="11" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C167" s="12" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D167" s="17" t="s">
-        <v>426</v>
+        <v>197</v>
       </c>
       <c r="E167" s="11" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F167" s="11">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="G167" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H167" s="11" t="s">
         <v>71</v>
@@ -9126,25 +8956,25 @@
     </row>
     <row r="168" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="11" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D168" s="17" t="s">
-        <v>428</v>
+        <v>200</v>
       </c>
       <c r="E168" s="11" t="s">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="F168" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G168" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H168" s="11" t="s">
         <v>71</v>
@@ -9154,25 +8984,25 @@
     </row>
     <row r="169" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="11" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D169" s="17" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="E169" s="11" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="F169" s="11">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G169" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H169" s="11" t="s">
         <v>71</v>
@@ -9182,22 +9012,22 @@
     </row>
     <row r="170" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="11" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C170" s="12" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="D170" s="17" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="E170" s="11" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F170" s="11">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G170" s="12" t="s">
         <v>15</v>
@@ -9210,25 +9040,25 @@
     </row>
     <row r="171" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="11" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B171" s="11" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C171" s="12" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="D171" s="17" t="s">
-        <v>200</v>
+        <v>427</v>
       </c>
       <c r="E171" s="11" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="F171" s="11">
         <v>0.5</v>
       </c>
       <c r="G171" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H171" s="11" t="s">
         <v>71</v>
@@ -9238,25 +9068,25 @@
     </row>
     <row r="172" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="11" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B172" s="11" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C172" s="12" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="D172" s="17" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="E172" s="11" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="F172" s="11">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G172" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H172" s="11" t="s">
         <v>71</v>
@@ -9266,25 +9096,25 @@
     </row>
     <row r="173" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="11" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B173" s="11" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="C173" s="12" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D173" s="17" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E173" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F173" s="11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G173" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H173" s="11" t="s">
         <v>71</v>
@@ -9294,25 +9124,25 @@
     </row>
     <row r="174" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="11" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B174" s="11" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="C174" s="12" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D174" s="17" t="s">
-        <v>436</v>
+        <v>241</v>
       </c>
       <c r="E174" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F174" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G174" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H174" s="11" t="s">
         <v>71</v>
@@ -9322,25 +9152,25 @@
     </row>
     <row r="175" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="11" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B175" s="11" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="C175" s="12" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D175" s="17" t="s">
-        <v>210</v>
+        <v>433</v>
       </c>
       <c r="E175" s="11" t="s">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="F175" s="11">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G175" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H175" s="11" t="s">
         <v>71</v>
@@ -9350,25 +9180,25 @@
     </row>
     <row r="176" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="11" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B176" s="11" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D176" s="17" t="s">
-        <v>439</v>
+        <v>194</v>
       </c>
       <c r="E176" s="11" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="F176" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G176" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H176" s="11" t="s">
         <v>71</v>
@@ -9378,19 +9208,19 @@
     </row>
     <row r="177" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="11" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B177" s="11" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D177" s="17" t="s">
-        <v>441</v>
+        <v>197</v>
       </c>
       <c r="E177" s="11" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="F177" s="11">
         <v>0.75</v>
@@ -9406,25 +9236,25 @@
     </row>
     <row r="178" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="11" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D178" s="17" t="s">
-        <v>443</v>
+        <v>200</v>
       </c>
       <c r="E178" s="11" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="F178" s="11">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="G178" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H178" s="11" t="s">
         <v>71</v>
@@ -9434,25 +9264,25 @@
     </row>
     <row r="179" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="11" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="B179" s="11" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="C179" s="12" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D179" s="17" t="s">
-        <v>218</v>
+        <v>438</v>
       </c>
       <c r="E179" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F179" s="11">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G179" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H179" s="11" t="s">
         <v>71</v>
@@ -9462,25 +9292,25 @@
     </row>
     <row r="180" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="11" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="C180" s="12" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D180" s="17" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E180" s="11" t="s">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="F180" s="11">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="G180" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H180" s="11" t="s">
         <v>71</v>
@@ -9490,19 +9320,19 @@
     </row>
     <row r="181" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="11" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="C181" s="12" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D181" s="17" t="s">
-        <v>194</v>
+        <v>442</v>
       </c>
       <c r="E181" s="11" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="F181" s="11">
         <v>1</v>
@@ -9518,25 +9348,25 @@
     </row>
     <row r="182" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="11" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D182" s="17" t="s">
-        <v>197</v>
+        <v>444</v>
       </c>
       <c r="E182" s="11" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F182" s="11">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G182" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H182" s="11" t="s">
         <v>71</v>
@@ -9546,25 +9376,25 @@
     </row>
     <row r="183" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="11" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B183" s="11" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D183" s="17" t="s">
-        <v>200</v>
+        <v>446</v>
       </c>
       <c r="E183" s="11" t="s">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="F183" s="11">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="G183" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H183" s="11" t="s">
         <v>71</v>
@@ -9574,25 +9404,25 @@
     </row>
     <row r="184" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="11" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B184" s="11" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D184" s="17" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E184" s="11" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F184" s="11">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G184" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H184" s="11" t="s">
         <v>71</v>
@@ -9602,25 +9432,25 @@
     </row>
     <row r="185" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="11" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B185" s="11" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D185" s="17" t="s">
-        <v>452</v>
+        <v>197</v>
       </c>
       <c r="E185" s="11" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="F185" s="11">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G185" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H185" s="11" t="s">
         <v>71</v>
@@ -9630,25 +9460,25 @@
     </row>
     <row r="186" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="11" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C186" s="12" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D186" s="17" t="s">
-        <v>454</v>
+        <v>200</v>
       </c>
       <c r="E186" s="11" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="F186" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G186" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H186" s="11" t="s">
         <v>71</v>
@@ -9658,22 +9488,22 @@
     </row>
     <row r="187" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="11" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D187" s="17" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E187" s="11" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="F187" s="11">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="G187" s="12" t="s">
         <v>15</v>
@@ -9686,25 +9516,25 @@
     </row>
     <row r="188" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="11" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C188" s="12" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D188" s="17" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="E188" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F188" s="11">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G188" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H188" s="11" t="s">
         <v>71</v>
@@ -9714,25 +9544,25 @@
     </row>
     <row r="189" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="11" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B189" s="11" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D189" s="17" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E189" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F189" s="11">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G189" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H189" s="11" t="s">
         <v>71</v>
@@ -9742,22 +9572,22 @@
     </row>
     <row r="190" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="11" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B190" s="11" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D190" s="17" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="E190" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F190" s="11">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G190" s="12" t="s">
         <v>17</v>
@@ -9770,25 +9600,25 @@
     </row>
     <row r="191" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="11" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C191" s="12" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D191" s="17" t="s">
-        <v>218</v>
+        <v>458</v>
       </c>
       <c r="E191" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F191" s="11">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G191" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H191" s="11" t="s">
         <v>71</v>
@@ -9798,25 +9628,25 @@
     </row>
     <row r="192" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="11" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D192" s="17" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E192" s="11" t="s">
         <v>77</v>
       </c>
       <c r="F192" s="11">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="G192" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H192" s="11" t="s">
         <v>71</v>
@@ -9826,13 +9656,13 @@
     </row>
     <row r="193" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="11" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B193" s="11" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D193" s="17" t="s">
         <v>194</v>
@@ -9844,7 +9674,7 @@
         <v>1</v>
       </c>
       <c r="G193" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H193" s="11" t="s">
         <v>71</v>
@@ -9854,13 +9684,13 @@
     </row>
     <row r="194" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="11" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C194" s="12" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D194" s="17" t="s">
         <v>197</v>
@@ -9882,13 +9712,13 @@
     </row>
     <row r="195" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="11" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B195" s="11" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C195" s="12" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D195" s="17" t="s">
         <v>200</v>
@@ -9910,13 +9740,13 @@
     </row>
     <row r="196" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="11" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C196" s="12" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D196" s="17" t="s">
         <v>203</v>
@@ -9938,25 +9768,25 @@
     </row>
     <row r="197" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="11" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B197" s="11" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C197" s="12" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D197" s="17" t="s">
-        <v>239</v>
+        <v>316</v>
       </c>
       <c r="E197" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F197" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G197" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H197" s="11" t="s">
         <v>71</v>
@@ -9966,16 +9796,16 @@
     </row>
     <row r="198" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="11" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B198" s="11" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C198" s="12" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D198" s="17" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E198" s="11" t="s">
         <v>176</v>
@@ -9984,7 +9814,7 @@
         <v>0.5</v>
       </c>
       <c r="G198" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H198" s="11" t="s">
         <v>71</v>
@@ -9994,16 +9824,16 @@
     </row>
     <row r="199" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="11" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D199" s="17" t="s">
-        <v>210</v>
+        <v>469</v>
       </c>
       <c r="E199" s="11" t="s">
         <v>176</v>
@@ -10012,7 +9842,7 @@
         <v>0.5</v>
       </c>
       <c r="G199" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H199" s="11" t="s">
         <v>71</v>
@@ -10022,25 +9852,25 @@
     </row>
     <row r="200" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="11" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B200" s="11" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D200" s="17" t="s">
-        <v>474</v>
+        <v>323</v>
       </c>
       <c r="E200" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F200" s="11">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G200" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H200" s="11" t="s">
         <v>71</v>
@@ -10050,22 +9880,22 @@
     </row>
     <row r="201" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="11" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D201" s="17" t="s">
-        <v>245</v>
+        <v>472</v>
       </c>
       <c r="E201" s="11" t="s">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="F201" s="11">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G201" s="12" t="s">
         <v>19</v>
@@ -10078,22 +9908,22 @@
     </row>
     <row r="202" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="11" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B202" s="11" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C202" s="12" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D202" s="17" t="s">
-        <v>477</v>
+        <v>194</v>
       </c>
       <c r="E202" s="11" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F202" s="11">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G202" s="12" t="s">
         <v>17</v>
@@ -10106,25 +9936,25 @@
     </row>
     <row r="203" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="11" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B203" s="11" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D203" s="17" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="E203" s="11" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F203" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G203" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H203" s="11" t="s">
         <v>71</v>
@@ -10134,25 +9964,25 @@
     </row>
     <row r="204" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="11" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B204" s="11" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D204" s="17" t="s">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="E204" s="11" t="s">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="F204" s="11">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="G204" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H204" s="11" t="s">
         <v>71</v>
@@ -10160,986 +9990,41 @@
       <c r="I204" s="11"/>
       <c r="J204" s="12"/>
     </row>
-    <row r="205" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="11" t="s">
-        <v>481</v>
-      </c>
-      <c r="B205" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C205" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D205" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="E205" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="F205" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="G205" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H205" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I205" s="11"/>
-      <c r="J205" s="12"/>
-    </row>
-    <row r="206" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="11" t="s">
-        <v>482</v>
-      </c>
-      <c r="B206" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C206" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D206" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="E206" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="F206" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="G206" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H206" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I206" s="11"/>
-      <c r="J206" s="12"/>
-    </row>
-    <row r="207" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="11" t="s">
-        <v>483</v>
-      </c>
-      <c r="B207" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C207" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D207" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="E207" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F207" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="G207" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H207" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I207" s="11"/>
-      <c r="J207" s="12"/>
-    </row>
-    <row r="208" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="11" t="s">
-        <v>484</v>
-      </c>
-      <c r="B208" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C208" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D208" s="17" t="s">
-        <v>485</v>
-      </c>
-      <c r="E208" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F208" s="11">
-        <v>1</v>
-      </c>
-      <c r="G208" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H208" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I208" s="11"/>
-      <c r="J208" s="12"/>
-    </row>
-    <row r="209" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="B209" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C209" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D209" s="17" t="s">
-        <v>487</v>
-      </c>
-      <c r="E209" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F209" s="11">
-        <v>1</v>
-      </c>
-      <c r="G209" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H209" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I209" s="11"/>
-      <c r="J209" s="12"/>
-    </row>
-    <row r="210" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="B210" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C210" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D210" s="17" t="s">
-        <v>489</v>
-      </c>
-      <c r="E210" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F210" s="11">
-        <v>1</v>
-      </c>
-      <c r="G210" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H210" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I210" s="11"/>
-      <c r="J210" s="12"/>
-    </row>
-    <row r="211" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="B211" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C211" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D211" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="E211" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F211" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="G211" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H211" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I211" s="11"/>
-      <c r="J211" s="12"/>
-    </row>
-    <row r="212" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="B212" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C212" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D212" s="17" t="s">
-        <v>493</v>
-      </c>
-      <c r="E212" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F212" s="11">
-        <v>1.5</v>
-      </c>
-      <c r="G212" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H212" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I212" s="11"/>
-      <c r="J212" s="12"/>
-    </row>
-    <row r="213" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="B213" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C213" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D213" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="E213" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F213" s="11">
-        <v>1.25</v>
-      </c>
-      <c r="G213" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H213" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I213" s="11"/>
-      <c r="J213" s="12"/>
-    </row>
-    <row r="214" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="11" t="s">
-        <v>495</v>
-      </c>
-      <c r="B214" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C214" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D214" s="17" t="s">
-        <v>496</v>
-      </c>
-      <c r="E214" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F214" s="11">
-        <v>2.5</v>
-      </c>
-      <c r="G214" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H214" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I214" s="11"/>
-      <c r="J214" s="12"/>
-    </row>
-    <row r="215" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="B215" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C215" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D215" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="E215" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="F215" s="11">
-        <v>1</v>
-      </c>
-      <c r="G215" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H215" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I215" s="11"/>
-      <c r="J215" s="12"/>
-    </row>
-    <row r="216" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="11" t="s">
-        <v>498</v>
-      </c>
-      <c r="B216" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C216" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D216" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="E216" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="F216" s="11">
-        <v>1.25</v>
-      </c>
-      <c r="G216" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H216" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I216" s="11"/>
-      <c r="J216" s="12"/>
-    </row>
-    <row r="217" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="11" t="s">
-        <v>499</v>
-      </c>
-      <c r="B217" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C217" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D217" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="E217" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F217" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="G217" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H217" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I217" s="11"/>
-      <c r="J217" s="12"/>
-    </row>
-    <row r="218" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="11" t="s">
-        <v>500</v>
-      </c>
-      <c r="B218" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C218" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D218" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="E218" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="F218" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="G218" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H218" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I218" s="11"/>
-      <c r="J218" s="12"/>
-    </row>
-    <row r="219" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="11" t="s">
-        <v>501</v>
-      </c>
-      <c r="B219" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C219" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="D219" s="17" t="s">
-        <v>502</v>
-      </c>
-      <c r="E219" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F219" s="11">
-        <v>1</v>
-      </c>
-      <c r="G219" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H219" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I219" s="11"/>
-      <c r="J219" s="12"/>
-    </row>
-    <row r="220" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="11" t="s">
-        <v>503</v>
-      </c>
-      <c r="B220" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C220" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="D220" s="17" t="s">
-        <v>504</v>
-      </c>
-      <c r="E220" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F220" s="11">
-        <v>1</v>
-      </c>
-      <c r="G220" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H220" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I220" s="11"/>
-      <c r="J220" s="12"/>
-    </row>
-    <row r="221" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="11" t="s">
-        <v>505</v>
-      </c>
-      <c r="B221" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C221" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="D221" s="17" t="s">
-        <v>506</v>
-      </c>
-      <c r="E221" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F221" s="11">
-        <v>1</v>
-      </c>
-      <c r="G221" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H221" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I221" s="11"/>
-      <c r="J221" s="12"/>
-    </row>
-    <row r="222" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="11" t="s">
-        <v>507</v>
-      </c>
-      <c r="B222" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C222" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="D222" s="17" t="s">
-        <v>508</v>
-      </c>
-      <c r="E222" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F222" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="G222" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H222" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I222" s="11"/>
-      <c r="J222" s="12"/>
-    </row>
-    <row r="223" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="11" t="s">
-        <v>509</v>
-      </c>
-      <c r="B223" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C223" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="D223" s="17" t="s">
-        <v>510</v>
-      </c>
-      <c r="E223" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F223" s="11">
-        <v>1.5</v>
-      </c>
-      <c r="G223" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H223" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I223" s="11"/>
-      <c r="J223" s="12"/>
-    </row>
-    <row r="224" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="11" t="s">
-        <v>511</v>
-      </c>
-      <c r="B224" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C224" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="D224" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="E224" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F224" s="11">
-        <v>1.25</v>
-      </c>
-      <c r="G224" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H224" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I224" s="11"/>
-      <c r="J224" s="12"/>
-    </row>
-    <row r="225" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="11" t="s">
-        <v>512</v>
-      </c>
-      <c r="B225" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C225" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="D225" s="17" t="s">
-        <v>513</v>
-      </c>
-      <c r="E225" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F225" s="11">
-        <v>2.5</v>
-      </c>
-      <c r="G225" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H225" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I225" s="11"/>
-      <c r="J225" s="12"/>
-    </row>
-    <row r="226" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="11" t="s">
-        <v>514</v>
-      </c>
-      <c r="B226" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C226" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="D226" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="E226" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="F226" s="11">
-        <v>1</v>
-      </c>
-      <c r="G226" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H226" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I226" s="11"/>
-      <c r="J226" s="12"/>
-    </row>
-    <row r="227" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="11" t="s">
-        <v>515</v>
-      </c>
-      <c r="B227" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C227" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="D227" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="E227" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="F227" s="11">
-        <v>1.25</v>
-      </c>
-      <c r="G227" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H227" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I227" s="11"/>
-      <c r="J227" s="12"/>
-    </row>
-    <row r="228" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="11" t="s">
-        <v>516</v>
-      </c>
-      <c r="B228" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C228" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="D228" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="E228" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F228" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="G228" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H228" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I228" s="11"/>
-      <c r="J228" s="12"/>
-    </row>
-    <row r="229" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="11" t="s">
-        <v>517</v>
-      </c>
-      <c r="B229" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C229" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="D229" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="E229" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="F229" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="G229" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H229" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I229" s="11"/>
-      <c r="J229" s="12"/>
-    </row>
-    <row r="230" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="11" t="s">
-        <v>518</v>
-      </c>
-      <c r="B230" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C230" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D230" s="17" t="s">
-        <v>337</v>
-      </c>
-      <c r="E230" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F230" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="G230" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H230" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I230" s="11"/>
-      <c r="J230" s="12"/>
-    </row>
-    <row r="231" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="11" t="s">
-        <v>519</v>
-      </c>
-      <c r="B231" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C231" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D231" s="17" t="s">
-        <v>520</v>
-      </c>
-      <c r="E231" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F231" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="G231" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H231" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I231" s="11"/>
-      <c r="J231" s="12"/>
-    </row>
-    <row r="232" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="11" t="s">
-        <v>521</v>
-      </c>
-      <c r="B232" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C232" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D232" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="E232" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F232" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="G232" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H232" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I232" s="11"/>
-      <c r="J232" s="12"/>
-    </row>
-    <row r="233" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="11" t="s">
-        <v>523</v>
-      </c>
-      <c r="B233" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C233" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D233" s="17" t="s">
-        <v>344</v>
-      </c>
-      <c r="E233" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F233" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="G233" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H233" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I233" s="11"/>
-      <c r="J233" s="12"/>
-    </row>
-    <row r="234" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="11" t="s">
-        <v>524</v>
-      </c>
-      <c r="B234" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C234" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D234" s="17" t="s">
-        <v>525</v>
-      </c>
-      <c r="E234" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F234" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="G234" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H234" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I234" s="11"/>
-      <c r="J234" s="12"/>
-    </row>
-    <row r="235" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="11" t="s">
-        <v>526</v>
-      </c>
-      <c r="B235" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C235" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D235" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="E235" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F235" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="G235" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H235" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I235" s="11"/>
-      <c r="J235" s="12"/>
-    </row>
-    <row r="236" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="11" t="s">
-        <v>527</v>
-      </c>
-      <c r="B236" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C236" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D236" s="17" t="s">
-        <v>528</v>
-      </c>
-      <c r="E236" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F236" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="G236" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H236" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I236" s="11"/>
-      <c r="J236" s="12"/>
-    </row>
-    <row r="237" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="11" t="s">
-        <v>529</v>
-      </c>
-      <c r="B237" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C237" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D237" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="E237" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="F237" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="G237" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H237" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I237" s="11"/>
-      <c r="J237" s="12"/>
-    </row>
-    <row r="238" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="B238" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C238" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D238" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="E238" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="F238" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="G238" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H238" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I238" s="11"/>
-      <c r="J238" s="12"/>
-    </row>
-    <row r="239" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="11" t="s">
-        <v>531</v>
-      </c>
-      <c r="B239" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C239" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D239" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="E239" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F239" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="G239" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H239" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I239" s="11"/>
-      <c r="J239" s="12"/>
-    </row>
+    <row r="205" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="55.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="55.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="55.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="41.4" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A5:J156" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="2">
@@ -11163,8 +10048,13 @@
       <formula>"Bloqueada"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G6:H239" xr:uid="{00000000-0002-0000-0200-000000000000}"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Responsable no valido" error="Elige a alguien del equipo: Bryan Chávez, Catalina Pescio o Emilio Fuentes." sqref="G6:G204" xr:uid="{00000000-0002-0000-0200-000000000000}">
+      <formula1>"Bryan Chávez,Catalina Pescio,Emilio Fuentes"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Estado no valido" error="Estados: Por hacer, En curso, En revisión, Terminada, Bloqueada o Descartada." sqref="H6:H204" xr:uid="{00000000-0002-0000-0200-000001000000}">
+      <formula1>"Por hacer,En curso,En revisión,Terminada,Bloqueada,Descartada"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -11192,7 +10082,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
-        <v>532</v>
+        <v>476</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -11202,7 +10092,7 @@
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
-        <v>533</v>
+        <v>477</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -11218,16 +10108,16 @@
         <v>169</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>534</v>
+        <v>478</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>535</v>
+        <v>479</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>536</v>
+        <v>480</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>537</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11241,13 +10131,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>538</v>
+        <v>482</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>539</v>
+        <v>483</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11261,13 +10151,13 @@
         <v>2</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>541</v>
+        <v>485</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>542</v>
+        <v>486</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11281,13 +10171,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>543</v>
+        <v>487</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>544</v>
+        <v>488</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11301,13 +10191,13 @@
         <v>4</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>545</v>
+        <v>489</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>546</v>
+        <v>490</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11321,13 +10211,13 @@
         <v>5</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>547</v>
+        <v>491</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>548</v>
+        <v>492</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11341,13 +10231,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>549</v>
+        <v>493</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>550</v>
+        <v>494</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11361,13 +10251,13 @@
         <v>2</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>551</v>
+        <v>495</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>552</v>
+        <v>496</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11381,13 +10271,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>553</v>
+        <v>497</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>554</v>
+        <v>498</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11401,13 +10291,13 @@
         <v>4</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>555</v>
+        <v>499</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>556</v>
+        <v>500</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11421,13 +10311,13 @@
         <v>1</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>557</v>
+        <v>501</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>558</v>
+        <v>502</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11441,13 +10331,13 @@
         <v>2</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>559</v>
+        <v>503</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>560</v>
+        <v>504</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11461,13 +10351,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>561</v>
+        <v>505</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>562</v>
+        <v>506</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11481,13 +10371,13 @@
         <v>4</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>563</v>
+        <v>507</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>564</v>
+        <v>508</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11501,13 +10391,13 @@
         <v>1</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>565</v>
+        <v>509</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>566</v>
+        <v>510</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11521,13 +10411,13 @@
         <v>2</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>567</v>
+        <v>511</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>568</v>
+        <v>512</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11541,13 +10431,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>569</v>
+        <v>513</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>570</v>
+        <v>514</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11561,13 +10451,13 @@
         <v>1</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>571</v>
+        <v>515</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>572</v>
+        <v>516</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11581,13 +10471,13 @@
         <v>2</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>573</v>
+        <v>517</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>574</v>
+        <v>518</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11601,13 +10491,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>575</v>
+        <v>519</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>576</v>
+        <v>520</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11621,13 +10511,13 @@
         <v>4</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>577</v>
+        <v>521</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>578</v>
+        <v>522</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11641,13 +10531,13 @@
         <v>5</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>579</v>
+        <v>523</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>580</v>
+        <v>524</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11661,13 +10551,13 @@
         <v>6</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>581</v>
+        <v>525</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>582</v>
+        <v>526</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11681,13 +10571,13 @@
         <v>7</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>583</v>
+        <v>527</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>584</v>
+        <v>528</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11701,13 +10591,13 @@
         <v>1</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>585</v>
+        <v>529</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>586</v>
+        <v>530</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.3">
@@ -11721,13 +10611,13 @@
         <v>2</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>587</v>
+        <v>531</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>588</v>
+        <v>532</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11741,13 +10631,13 @@
         <v>3</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>589</v>
+        <v>533</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>590</v>
+        <v>534</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11761,13 +10651,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>591</v>
+        <v>535</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>592</v>
+        <v>536</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11781,13 +10671,13 @@
         <v>2</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>593</v>
+        <v>537</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>594</v>
+        <v>538</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11801,13 +10691,13 @@
         <v>3</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>595</v>
+        <v>539</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>596</v>
+        <v>540</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11821,13 +10711,13 @@
         <v>1</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>597</v>
+        <v>541</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>598</v>
+        <v>542</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11841,13 +10731,13 @@
         <v>2</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>599</v>
+        <v>543</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>600</v>
+        <v>544</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11861,13 +10751,13 @@
         <v>3</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>601</v>
+        <v>545</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>602</v>
+        <v>546</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11881,13 +10771,13 @@
         <v>1</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>603</v>
+        <v>547</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>604</v>
+        <v>548</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11901,13 +10791,13 @@
         <v>2</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>605</v>
+        <v>549</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>606</v>
+        <v>550</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11921,13 +10811,13 @@
         <v>3</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>607</v>
+        <v>551</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>608</v>
+        <v>552</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11941,13 +10831,13 @@
         <v>1</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>609</v>
+        <v>553</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>610</v>
+        <v>554</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11961,13 +10851,13 @@
         <v>2</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>611</v>
+        <v>555</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>612</v>
+        <v>556</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -11981,13 +10871,13 @@
         <v>3</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>613</v>
+        <v>557</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>614</v>
+        <v>558</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12001,13 +10891,13 @@
         <v>4</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>615</v>
+        <v>559</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>616</v>
+        <v>560</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -12021,13 +10911,13 @@
         <v>1</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>617</v>
+        <v>561</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>618</v>
+        <v>562</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -12041,13 +10931,13 @@
         <v>2</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>619</v>
+        <v>563</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>620</v>
+        <v>564</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12061,13 +10951,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>621</v>
+        <v>565</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>622</v>
+        <v>566</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -12081,13 +10971,13 @@
         <v>1</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>623</v>
+        <v>567</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>624</v>
+        <v>568</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12101,13 +10991,13 @@
         <v>2</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>625</v>
+        <v>569</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>626</v>
+        <v>570</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12121,13 +11011,13 @@
         <v>3</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>627</v>
+        <v>571</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>628</v>
+        <v>572</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12141,13 +11031,13 @@
         <v>4</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>629</v>
+        <v>573</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>630</v>
+        <v>574</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -12161,13 +11051,13 @@
         <v>1</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>631</v>
+        <v>575</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>632</v>
+        <v>576</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12181,13 +11071,13 @@
         <v>2</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>633</v>
+        <v>577</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>634</v>
+        <v>578</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -12201,13 +11091,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>635</v>
+        <v>579</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>636</v>
+        <v>580</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12221,13 +11111,13 @@
         <v>1</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>637</v>
+        <v>581</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>638</v>
+        <v>582</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12241,13 +11131,13 @@
         <v>2</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>639</v>
+        <v>583</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>640</v>
+        <v>584</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -12261,13 +11151,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>641</v>
+        <v>585</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>642</v>
+        <v>586</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -12281,13 +11171,13 @@
         <v>1</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>643</v>
+        <v>587</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>644</v>
+        <v>588</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -12301,13 +11191,13 @@
         <v>2</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>645</v>
+        <v>589</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>646</v>
+        <v>590</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -12321,13 +11211,13 @@
         <v>3</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>647</v>
+        <v>591</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>648</v>
+        <v>592</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12341,13 +11231,13 @@
         <v>1</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>649</v>
+        <v>593</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>650</v>
+        <v>594</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12361,13 +11251,13 @@
         <v>2</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>651</v>
+        <v>595</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>652</v>
+        <v>596</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12381,13 +11271,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>653</v>
+        <v>597</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>654</v>
+        <v>598</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -12401,13 +11291,13 @@
         <v>1</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>655</v>
+        <v>599</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>656</v>
+        <v>600</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12421,13 +11311,13 @@
         <v>2</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>657</v>
+        <v>601</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>658</v>
+        <v>602</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -12441,13 +11331,13 @@
         <v>1</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>659</v>
+        <v>603</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>660</v>
+        <v>604</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12461,13 +11351,13 @@
         <v>2</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>661</v>
+        <v>605</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>662</v>
+        <v>606</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -12481,13 +11371,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>663</v>
+        <v>607</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>664</v>
+        <v>608</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12501,13 +11391,13 @@
         <v>4</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>665</v>
+        <v>609</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>666</v>
+        <v>610</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -12521,13 +11411,13 @@
         <v>1</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>667</v>
+        <v>611</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>668</v>
+        <v>612</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12541,13 +11431,13 @@
         <v>2</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>669</v>
+        <v>613</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>670</v>
+        <v>614</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12561,13 +11451,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>671</v>
+        <v>615</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>672</v>
+        <v>616</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12581,13 +11471,13 @@
         <v>1</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>673</v>
+        <v>617</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>674</v>
+        <v>618</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12601,13 +11491,13 @@
         <v>2</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>675</v>
+        <v>619</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>676</v>
+        <v>620</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -12651,7 +11541,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
-        <v>677</v>
+        <v>621</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -12659,7 +11549,7 @@
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
-        <v>678</v>
+        <v>622</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -12667,16 +11557,16 @@
     </row>
     <row r="4" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>534</v>
+        <v>478</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>679</v>
+        <v>623</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>680</v>
+        <v>624</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>681</v>
+        <v>625</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -12684,13 +11574,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>682</v>
+        <v>626</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>683</v>
+        <v>627</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -12701,10 +11591,10 @@
         <v>195</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>684</v>
+        <v>628</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -12712,13 +11602,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>685</v>
+        <v>629</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>686</v>
+        <v>630</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -12726,13 +11616,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>687</v>
+        <v>631</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>688</v>
+        <v>632</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -12740,13 +11630,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>689</v>
+        <v>633</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>690</v>
+        <v>634</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -12754,13 +11644,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>691</v>
+        <v>635</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>692</v>
+        <v>636</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -12768,13 +11658,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>693</v>
+        <v>637</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>694</v>
+        <v>638</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -12785,10 +11675,10 @@
         <v>198</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>695</v>
+        <v>639</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -12796,13 +11686,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>696</v>
+        <v>640</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>697</v>
+        <v>641</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -12813,15 +11703,15 @@
         <v>201</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>698</v>
+        <v>642</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
-        <v>699</v>
+        <v>643</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
